--- a/extra/report/No.追加実習_ユーザー認証_テスト結果.xlsx
+++ b/extra/report/No.追加実習_ユーザー認証_テスト結果.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864650E2-A6DA-4CC2-9545-D67678064F2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFE45FF-7680-4D1F-B989-7E42E34F2C73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>・データーベースに料金テーブル「T_ACCOUNT」作成済み</t>
     <phoneticPr fontId="1"/>
@@ -86,6 +86,39 @@
     </rPh>
     <rPh sb="40" eb="42">
       <t>イミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>■パスワード作成方法</t>
+    <rPh sb="6" eb="10">
+      <t>サクセイホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Linux環境のWSL2で「htpsswd -nB -C 10 &lt;ユーザー名&gt;」→パスワードを２回入力で作成する</t>
+    <rPh sb="5" eb="7">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>こうすることでハッシュ化ができる</t>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1660,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CFDC69E-3E2C-4572-B64E-F2DD85F512B2}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.15">
@@ -1676,6 +1709,21 @@
     <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B13" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/extra/report/No.追加実習_ユーザー認証_テスト結果.xlsx
+++ b/extra/report/No.追加実習_ユーザー認証_テスト結果.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFE45FF-7680-4D1F-B989-7E42E34F2C73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B64A47D-F881-4D67-8234-EA2E357A390E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,28 +97,28 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Linux環境のWSL2で「htpsswd -nB -C 10 &lt;ユーザー名&gt;」→パスワードを２回入力で作成する</t>
-    <rPh sb="5" eb="7">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サクセイ</t>
+    <t>こうすることでハッシュ化ができる</t>
+    <rPh sb="11" eb="12">
+      <t>カ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>こうすることでハッシュ化ができる</t>
-    <rPh sb="11" eb="12">
-      <t>カ</t>
+    <t>Linux環境のWSL2で「htpasswd -nB -C 10 &lt;ユーザー名&gt;」→パスワードを２回入力で作成する</t>
+    <rPh sb="5" eb="7">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1718,12 +1718,12 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1850,18 +1850,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2023,18 +2023,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
